--- a/data/S1982_83_FINAL.xlsx
+++ b/data/S1982_83_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +80,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15138,7 +15156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15214,6 +15232,47 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1982_83_0030 'TJ Baník ČSA Karviná' prev→CLUB_S1981_82_0035 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1982_83_0052 'Slávia Ekonóm Bratislava' prev→CLUB_S1981_82_0486 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0016</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1982_83_0016 'Kvalifikace o postup do II. ligy' (L25, parent=NODE_S1982_83_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -44736,6 +44795,127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0030</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0030 'TJ Baník ČSA Karviná' prev→CLUB_S1981_82_0035 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0052</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0052 'Slávia Ekonóm Bratislava' prev→CLUB_S1981_82_0486 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0016</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1982_83_0016 'Kvalifikace o postup do II. ligy' (L25, parent=NODE_S1982_83_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1982_83_FINAL.xlsx
+++ b/data/S1982_83_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15156,7 +15156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15238,7 +15238,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1982_83_0030 'TJ Baník ČSA Karviná' prev→CLUB_S1981_82_0035 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15250,7 +15250,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1982_83_0052 'Slávia Ekonóm Bratislava' prev→CLUB_S1981_82_0486 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15260,17 +15260,492 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1982_83_0016</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1982_83_0016 'Kvalifikace o postup do II. ligy' (L25, parent=NODE_S1982_83_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0035 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1981_82_0486 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Ekonóm Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0036 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ZNZZ Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -20775,12 +21250,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -21158,12 +21633,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -21326,12 +21801,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -21368,12 +21843,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -21578,12 +22053,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -21751,12 +22226,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -22003,12 +22478,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -22050,12 +22525,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -22134,12 +22609,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -22307,12 +22782,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -22564,12 +23039,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -22653,12 +23128,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -22690,12 +23165,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Bratislava = TJ Slávia Ekonóm Bratislava (Wiki D42 - registr ustavy 04/2026). Slovensky/Bratislavsky kraj. **Ekonóm** = Vysoká škola ekonomická (dnes EU Bratislava). Spravny pravopis 'Ekonóm' s diakritikou (drive 'Ekonom'). city Bratislava. || TBD: auto-prev_club_id oprava → CLUB_S1981_82_0486 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>Bratislava = TJ Slávia Ekonóm Bratislava (Wiki D42 - registr ustavy 04/2026). Slovensky/Bratislavsky kraj. **Ekonóm** = Vysoká škola ekonomická (dnes EU Bratislava). Spravny pravopis 'Ekonóm' s diakritikou (drive 'Ekonom'). city Bratislava. || TBD: auto-prev_club_id oprava → CLUB_S1981_82_0486 (weak, jméno+město; verifikovat) [fix_continuity] || TBD: city 'Slávia Ekonóm Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Slávia Ekonóm Bratislava</t>
+          <t>Bratislava</t>
         </is>
       </c>
     </row>
@@ -22937,12 +23412,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Praha-Žižkov = TJ Rudá Hvězda Žižkov (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 3. RH = Ruda hvezda (SNB). city Praha (Žižkov).</t>
+          <t>Praha-Žižkov = TJ Rudá Hvězda Žižkov (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 3. RH = Ruda hvezda (SNB). city Praha (Žižkov). || TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Rudá Hvězda Žižkov</t>
+          <t>Rudá Hvězda</t>
         </is>
       </c>
     </row>
@@ -24185,12 +24660,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -25611,12 +26086,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -25700,12 +26175,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -26590,12 +27065,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -28781,12 +29256,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -29110,12 +29585,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Cheb = TJ Lokomotiva depo Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Lokomotivni depo Cheb** = železničárský klub (drive vyznamne pohranicni depo, nejdulezitejsi prepojeni s NSR). city Cheb.</t>
+          <t>Cheb = TJ Lokomotiva depo Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Lokomotivni depo Cheb** = železničárský klub (drive vyznamne pohranicni depo, nejdulezitejsi prepojeni s NSR). city Cheb. || TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Lokomotiva depo Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -29827,12 +30302,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín.</t>
+          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Technické služby Děčín</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
@@ -30336,12 +30811,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -30588,12 +31063,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ ZNZZ Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **ZNZZ** = Zemědělsky nákupní zásobovací zaopatrovací podnik. city Česká Lípa.</t>
+          <t>Česká Lípa = TJ ZNZZ Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **ZNZZ** = Zemědělsky nákupní zásobovací zaopatrovací podnik. city Česká Lípa. || TBD: city 'ZNZZ Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>ZNZZ Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -30897,12 +31372,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -31248,12 +31723,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -31416,12 +31891,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ OSP Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). **OSP** = Okresní stavební podnik. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ OSP Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). **OSP** = Okresní stavební podnik. city Nový Bydžov. || TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>OSP Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -32588,12 +33063,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Pardubice = TJ Povodí Labe Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Povodí Labe** = státní podnik (správa labské vodní cesty). city Pardubice.</t>
+          <t>Pardubice = TJ Povodí Labe Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Povodí Labe** = státní podnik (správa labské vodní cesty). city Pardubice. || TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Povodí Labe Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -32682,12 +33157,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Pardubice = TJ SSM SNV Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **SSM** = Socialistický svaz mládeže, **SNV** = pravdepodobne 'Sbor narodni bezpecnosti' (= SNB - policejni klub). city Pardubice.</t>
+          <t>Pardubice = TJ SSM SNV Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **SSM** = Socialistický svaz mládeže, **SNV** = pravdepodobne 'Sbor narodni bezpecnosti' (= SNB - policejni klub). city Pardubice. || TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>SSM SNV Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -33570,12 +34045,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Pardubice = TJ Dopravní podnik Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Dopravní podnik** = mestske dopravce (MHD - autobusy, trolejbusy). city Pardubice.</t>
+          <t>Pardubice = TJ Dopravní podnik Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Dopravní podnik** = mestske dopravce (MHD - autobusy, trolejbusy). city Pardubice. || TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Dopravní podnik Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -34475,12 +34950,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -37416,12 +37891,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -37777,12 +38252,12 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>Olomouc = TJ Sigma ZTS Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Stejne jako ZTS Sigma - jiny poradi slov. city Olomouc.</t>
+          <t>Olomouc = TJ Sigma ZTS Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Stejne jako ZTS Sigma - jiny poradi slov. city Olomouc. || TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>Sigma ZTS Olomouc</t>
+          <t>Olomouc</t>
         </is>
       </c>
     </row>
@@ -44801,11 +45276,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -44850,21 +45325,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0030</t>
+          <t>CLUB_S1982_83_0004</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0030 'TJ Baník ČSA Karviná' prev→CLUB_S1981_82_0035 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -44872,21 +45345,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0052</t>
+          <t>CLUB_S1982_83_0013</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0052 'Slávia Ekonóm Bratislava' prev→CLUB_S1981_82_0486 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -44894,24 +45365,822 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1982_83_0016</t>
+          <t>CLUB_S1982_83_0017</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1982_83_0016 'Kvalifikace o postup do II. ligy' (L25, parent=NODE_S1982_83_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0018</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0023</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0027</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0030</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0035 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0033</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0034</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0036</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0040</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0046</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0048</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0052</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1981_82_0486 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0052</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slávia Ekonóm Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0060</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0060</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0067</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0036 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0090</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0124</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0126</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0126</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0146</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0194</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0201</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0218</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0224</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0230</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0236</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ZNZZ Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0241</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0244</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0252</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0256</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0264</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0282</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0284</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0303</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0325</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0336</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0349</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0356</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0395</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1982_83_0403</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1982_83_FINAL.xlsx
+++ b/data/S1982_83_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15156,7 +15156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15238,7 +15238,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15250,7 +15250,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15262,7 +15262,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15274,7 +15274,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0035 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15286,7 +15286,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15298,7 +15298,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15310,7 +15310,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0035 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -15322,7 +15322,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15346,7 +15346,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1981_82_0486 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15358,7 +15358,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Ekonóm Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15370,7 +15370,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15382,7 +15382,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15394,7 +15394,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1981_82_0486 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0036 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15406,7 +15406,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slávia Ekonóm Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15418,7 +15418,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15430,7 +15430,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -15442,7 +15442,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0036 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -15466,7 +15466,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -15478,7 +15478,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -15490,7 +15490,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -15502,7 +15502,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -15514,7 +15514,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ZNZZ Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -15526,7 +15526,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -15538,7 +15538,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -15550,7 +15550,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -15562,7 +15562,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -15574,7 +15574,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ZNZZ Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -15586,7 +15586,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -15598,7 +15598,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -15610,7 +15610,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -15622,7 +15622,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -15634,7 +15634,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -15646,7 +15646,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -15658,94 +15658,10 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -15762,7 +15678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15821,6 +15737,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15863,6 +15784,11 @@
           <t>12 týmů. Mistr: Dukla Jihlava.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15910,6 +15836,11 @@
           <t>Trenčín – Olomouc 3:0. 1. a 3. utkání doma; případné 5. utkání v Gottwaldově. Při nerozhodném výsledku 3×5 minut + nájezdy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15952,6 +15883,11 @@
           <t>I.ČNHL (2 sk. → finálová sk. + 2× o udržení + kvalifikace o 1. ČNHL) + SNHL (12). Kvalifikace o 1. CHL.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15994,6 +15930,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16036,6 +15977,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16078,6 +16024,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16120,6 +16071,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16162,6 +16118,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16204,6 +16165,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16246,6 +16212,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16288,6 +16259,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16330,6 +16306,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16372,6 +16353,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16414,6 +16400,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16565,6 +16556,11 @@
           <t>Ze společného přeboru Západoslovenského kraje a Bratislavy se účastnil nejlepší západoslovenský i bratislavský tým. ASVŠ Dukla Trenčín "B" hrála domácí utkání v Topoľčanech.</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0018</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16607,6 +16603,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0019</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16733,6 +16734,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0022</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16775,6 +16781,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0023</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16817,6 +16828,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0024</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16859,6 +16875,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16901,6 +16922,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16985,6 +17011,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17069,6 +17100,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0028</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17195,6 +17231,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0036</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -17368,6 +17409,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0035</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -17410,6 +17456,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0036</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17452,6 +17503,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0037</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -17494,6 +17550,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0038</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -17536,6 +17597,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0039</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -17704,6 +17770,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0040</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -17746,6 +17817,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0042</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -17788,6 +17864,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0043</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -17830,6 +17911,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0047</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17872,6 +17958,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0048</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -17914,6 +18005,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0049</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17956,6 +18052,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0050</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -18045,6 +18146,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0052</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -18087,6 +18193,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0053</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -18129,6 +18240,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0054</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -18171,6 +18287,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0055</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -18213,6 +18334,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0056</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -18255,6 +18381,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0057</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -18297,6 +18428,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0058</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -18339,6 +18475,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0057</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -18381,6 +18522,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0060</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -18423,6 +18569,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0061</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -18549,6 +18700,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0063</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18591,6 +18747,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0064</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18722,6 +18883,11 @@
           <t>Kvalifikace</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0067</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18764,6 +18930,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0070</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18806,6 +18977,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0071</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18848,6 +19024,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0076</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18890,6 +19071,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0077</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -19226,6 +19412,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0081</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -19310,6 +19501,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0082</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -19394,6 +19590,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0083</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -19436,6 +19637,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0084</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -19478,6 +19684,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0085</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19562,6 +19773,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0086</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19688,6 +19904,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0089</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19728,6 +19949,11 @@
       <c r="J93" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0090</t>
         </is>
       </c>
     </row>
@@ -21250,12 +21476,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -21801,12 +22027,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -22226,12 +22452,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -23039,12 +23265,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -26175,12 +26401,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -34950,12 +35176,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -37891,12 +38117,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -45276,7 +45502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -45330,12 +45556,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0004</t>
+          <t>CLUB_S1982_83_0013</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45350,12 +45576,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0013</t>
+          <t>CLUB_S1982_83_0018</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45370,12 +45596,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0017</t>
+          <t>CLUB_S1982_83_0023</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45390,12 +45616,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0018</t>
+          <t>CLUB_S1982_83_0030</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0035 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45410,12 +45636,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0023</t>
+          <t>CLUB_S1982_83_0033</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45430,12 +45656,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0027</t>
+          <t>CLUB_S1982_83_0034</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45450,12 +45676,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0030</t>
+          <t>CLUB_S1982_83_0036</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0035 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45470,12 +45696,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0033</t>
+          <t>CLUB_S1982_83_0040</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45490,12 +45716,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0034</t>
+          <t>CLUB_S1982_83_0048</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45510,12 +45736,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0036</t>
+          <t>CLUB_S1982_83_0052</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1981_82_0486 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45530,12 +45756,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0040</t>
+          <t>CLUB_S1982_83_0052</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slávia Ekonóm Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45550,12 +45776,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0046</t>
+          <t>CLUB_S1982_83_0060</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45570,12 +45796,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0048</t>
+          <t>CLUB_S1982_83_0060</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45590,12 +45816,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0052</t>
+          <t>CLUB_S1982_83_0067</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1981_82_0486 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0036 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45610,12 +45836,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0052</t>
+          <t>CLUB_S1982_83_0090</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slávia Ekonóm Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45630,12 +45856,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0060</t>
+          <t>CLUB_S1982_83_0124</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45650,12 +45876,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0060</t>
+          <t>CLUB_S1982_83_0126</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45670,12 +45896,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0067</t>
+          <t>CLUB_S1982_83_0146</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0036 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45690,12 +45916,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0090</t>
+          <t>CLUB_S1982_83_0194</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45710,12 +45936,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0124</t>
+          <t>CLUB_S1982_83_0201</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45730,12 +45956,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0126</t>
+          <t>CLUB_S1982_83_0218</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45750,12 +45976,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0126</t>
+          <t>CLUB_S1982_83_0224</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -45770,12 +45996,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0146</t>
+          <t>CLUB_S1982_83_0230</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45790,12 +46016,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0194</t>
+          <t>CLUB_S1982_83_0236</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'ZNZZ Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45810,12 +46036,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0201</t>
+          <t>CLUB_S1982_83_0241</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -45830,12 +46056,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0218</t>
+          <t>CLUB_S1982_83_0244</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45850,12 +46076,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0224</t>
+          <t>CLUB_S1982_83_0252</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45870,12 +46096,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0230</t>
+          <t>CLUB_S1982_83_0256</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45890,12 +46116,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0236</t>
+          <t>CLUB_S1982_83_0264</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'ZNZZ Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -45910,12 +46136,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0241</t>
+          <t>CLUB_S1982_83_0282</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45930,12 +46156,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0244</t>
+          <t>CLUB_S1982_83_0284</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45950,12 +46176,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0252</t>
+          <t>CLUB_S1982_83_0303</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45970,12 +46196,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0256</t>
+          <t>CLUB_S1982_83_0336</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -45990,12 +46216,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0264</t>
+          <t>CLUB_S1982_83_0349</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -46010,12 +46236,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0282</t>
+          <t>CLUB_S1982_83_0356</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -46030,157 +46256,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1982_83_0284</t>
+          <t>CLUB_S1982_83_0403</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1982_83_0303</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1982_83_0325</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1982_83_0336</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1982_83_0349</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1982_83_0356</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1982_83_0395</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1982_83_0403</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F44"/>
+  <autoFilter ref="A1:F37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1982_83_FINAL.xlsx
+++ b/data/S1982_83_FINAL.xlsx
@@ -15678,7 +15678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15740,6 +15740,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1982_83_FINAL.xlsx
+++ b/data/S1982_83_FINAL.xlsx
@@ -16024,6 +16024,16 @@
           <t>NODE_S1982_83_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16038,6 +16048,14 @@
         <is>
           <t>NODE_S1981_82_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -16071,6 +16089,8 @@
           <t>NODE_S1982_83_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16085,6 +16105,14 @@
         <is>
           <t>NODE_S1981_82_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -16118,6 +16146,8 @@
           <t>NODE_S1982_83_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16132,6 +16162,14 @@
         <is>
           <t>NODE_S1981_82_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -16306,6 +16344,8 @@
           <t>NODE_S1982_83_0004</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16320,6 +16360,14 @@
         <is>
           <t>NODE_S1981_82_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -16353,6 +16401,8 @@
           <t>NODE_S1982_83_0004</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16367,6 +16417,14 @@
         <is>
           <t>NODE_S1981_82_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -16400,6 +16458,12 @@
           <t>NODE_S1982_83_0005</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0012</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16414,6 +16478,14 @@
         <is>
           <t>NODE_S1981_82_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -16734,6 +16806,16 @@
           <t>NODE_S1982_83_0018</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0022</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0023</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16748,6 +16830,14 @@
         <is>
           <t>NODE_S1981_82_0022</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -16781,6 +16871,8 @@
           <t>NODE_S1982_83_0018</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16795,6 +16887,14 @@
         <is>
           <t>NODE_S1981_82_0023</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -16828,6 +16928,8 @@
           <t>NODE_S1982_83_0018</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16842,6 +16944,14 @@
         <is>
           <t>NODE_S1981_82_0024</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -16969,6 +17079,12 @@
           <t>NODE_S1982_83_0024</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0027</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16978,6 +17094,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -17011,6 +17135,8 @@
           <t>NODE_S1982_83_0024</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17025,6 +17151,14 @@
         <is>
           <t>NODE_S1981_82_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -17058,6 +17192,8 @@
           <t>NODE_S1982_83_0024</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17067,6 +17203,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -17409,6 +17553,8 @@
           <t>NODE_S1982_83_0024</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17423,6 +17569,14 @@
         <is>
           <t>NODE_S1981_82_0035</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -17644,6 +17798,12 @@
           <t>NODE_S1982_83_0039</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0042</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17653,6 +17813,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -17686,6 +17854,8 @@
           <t>NODE_S1982_83_0039</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17695,6 +17865,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -17728,6 +17906,8 @@
           <t>NODE_S1982_83_0039</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17737,6 +17917,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -18240,6 +18428,12 @@
           <t>NODE_S1982_83_0052</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0057</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18254,6 +18448,14 @@
         <is>
           <t>NODE_S1981_82_0054</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -18381,6 +18583,8 @@
           <t>NODE_S1982_83_0052</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18395,6 +18599,14 @@
         <is>
           <t>NODE_S1981_82_0057</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -18428,6 +18640,8 @@
           <t>NODE_S1982_83_0052</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18442,6 +18656,14 @@
         <is>
           <t>NODE_S1981_82_0058</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -18475,6 +18697,8 @@
           <t>NODE_S1982_83_0052</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18489,6 +18713,14 @@
         <is>
           <t>NODE_S1981_82_0057</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -18616,6 +18848,16 @@
           <t>NODE_S1982_83_0060</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0064</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0065</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18625,6 +18867,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -18658,6 +18908,16 @@
           <t>NODE_S1982_83_0060</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0064</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0065</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18667,6 +18927,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -18700,6 +18968,8 @@
           <t>NODE_S1982_83_0060</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18714,6 +18984,14 @@
         <is>
           <t>NODE_S1981_82_0063</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -18747,6 +19025,8 @@
           <t>NODE_S1982_83_0060</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18761,6 +19041,14 @@
         <is>
           <t>NODE_S1981_82_0064</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>1.–6. ZČ</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -19118,6 +19406,8 @@
           <t>NODE_S1982_83_0069</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19127,6 +19417,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -19160,6 +19458,8 @@
           <t>NODE_S1982_83_0069</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19169,6 +19469,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -19202,6 +19510,8 @@
           <t>NODE_S1982_83_0069</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19211,6 +19521,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -19370,6 +19688,8 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19379,6 +19699,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -19412,6 +19740,8 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19426,6 +19756,14 @@
         <is>
           <t>NODE_S1981_82_0081</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -19459,6 +19797,8 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19468,6 +19808,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -19501,6 +19849,8 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19515,6 +19865,14 @@
         <is>
           <t>NODE_S1981_82_0082</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -19548,6 +19906,8 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19557,6 +19917,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -19590,6 +19958,8 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19604,6 +19974,14 @@
         <is>
           <t>NODE_S1981_82_0083</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -19731,6 +20109,16 @@
           <t>NODE_S1982_83_0085</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0088</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0089</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19740,6 +20128,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -19773,6 +20169,8 @@
           <t>NODE_S1982_83_0085</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19787,6 +20185,14 @@
         <is>
           <t>NODE_S1981_82_0086</t>
         </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -19820,6 +20226,8 @@
           <t>NODE_S1982_83_0085</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19829,6 +20237,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>6.–9. ZČ</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -20166,6 +20582,8 @@
           <t>NODE_S1982_83_0104</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20175,6 +20593,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -20250,6 +20676,16 @@
           <t>NODE_S1982_83_0105</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0097</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0101</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20259,6 +20695,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -20292,6 +20736,8 @@
           <t>NODE_S1982_83_0105</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20301,6 +20747,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -20334,6 +20788,8 @@
           <t>NODE_S1982_83_0105</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20343,6 +20799,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="103">

--- a/data/S1982_83_FINAL.xlsx
+++ b/data/S1982_83_FINAL.xlsx
@@ -718,6 +718,11 @@
           <t>HC Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -16089,8 +16094,6 @@
           <t>NODE_S1982_83_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16146,8 +16149,6 @@
           <t>NODE_S1982_83_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16344,8 +16345,6 @@
           <t>NODE_S1982_83_0004</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16401,8 +16400,6 @@
           <t>NODE_S1982_83_0004</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16458,7 +16455,6 @@
           <t>NODE_S1982_83_0005</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>NODE_S1982_83_0012</t>
@@ -16871,8 +16867,6 @@
           <t>NODE_S1982_83_0018</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16928,8 +16922,6 @@
           <t>NODE_S1982_83_0018</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17084,7 +17076,6 @@
           <t>NODE_S1982_83_0027</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17135,8 +17126,6 @@
           <t>NODE_S1982_83_0024</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17192,8 +17181,6 @@
           <t>NODE_S1982_83_0024</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17553,8 +17540,6 @@
           <t>NODE_S1982_83_0024</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17803,7 +17788,6 @@
           <t>NODE_S1982_83_0042</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17854,8 +17838,6 @@
           <t>NODE_S1982_83_0039</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17906,8 +17888,6 @@
           <t>NODE_S1982_83_0039</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18433,7 +18413,6 @@
           <t>NODE_S1982_83_0057</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18583,8 +18562,6 @@
           <t>NODE_S1982_83_0052</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18640,8 +18617,6 @@
           <t>NODE_S1982_83_0052</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18697,8 +18672,6 @@
           <t>NODE_S1982_83_0052</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18968,8 +18941,6 @@
           <t>NODE_S1982_83_0060</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19025,8 +18996,6 @@
           <t>NODE_S1982_83_0060</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19406,8 +19375,6 @@
           <t>NODE_S1982_83_0069</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19458,8 +19425,6 @@
           <t>NODE_S1982_83_0069</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19510,8 +19475,6 @@
           <t>NODE_S1982_83_0069</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19688,8 +19651,6 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19740,8 +19701,6 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19797,8 +19756,6 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19849,8 +19806,6 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19906,8 +19861,6 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19958,8 +19911,6 @@
           <t>NODE_S1982_83_0107</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20169,8 +20120,6 @@
           <t>NODE_S1982_83_0085</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20226,8 +20175,6 @@
           <t>NODE_S1982_83_0085</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20582,8 +20529,6 @@
           <t>NODE_S1982_83_0104</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20736,8 +20681,6 @@
           <t>NODE_S1982_83_0105</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20788,8 +20731,6 @@
           <t>NODE_S1982_83_0105</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -40606,7 +40547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40834,6 +40775,18 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>Hlavní soutěže plně; krajské soutěže jako tabulková architektura; okresní / pravé zóny jen jako klubová evidence (L100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>

--- a/data/S1982_83_FINAL.xlsx
+++ b/data/S1982_83_FINAL.xlsx
@@ -38,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +57,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +89,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -98,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +119,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -52854,7 +52865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -52911,7 +52922,7 @@
           <t>CLUB_S1982_83_0013</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52931,7 +52942,7 @@
           <t>CLUB_S1982_83_0018</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52951,7 +52962,7 @@
           <t>CLUB_S1982_83_0023</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52971,7 +52982,7 @@
           <t>CLUB_S1982_83_0030</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0035 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -52991,7 +53002,7 @@
           <t>CLUB_S1982_83_0033</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53011,7 +53022,7 @@
           <t>CLUB_S1982_83_0034</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53031,7 +53042,7 @@
           <t>CLUB_S1982_83_0036</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53051,7 +53062,7 @@
           <t>CLUB_S1982_83_0040</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53071,7 +53082,7 @@
           <t>CLUB_S1982_83_0048</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53091,7 +53102,7 @@
           <t>CLUB_S1982_83_0052</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id oprava → CLUB_S1981_82_0486 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -53111,7 +53122,7 @@
           <t>CLUB_S1982_83_0052</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Slávia Ekonóm Bratislava' → 'Bratislava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53131,7 +53142,7 @@
           <t>CLUB_S1982_83_0060</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53151,7 +53162,7 @@
           <t>CLUB_S1982_83_0060</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -53171,7 +53182,7 @@
           <t>CLUB_S1982_83_0067</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1981_82_0036 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -53191,7 +53202,7 @@
           <t>CLUB_S1982_83_0090</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53211,7 +53222,7 @@
           <t>CLUB_S1982_83_0124</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53231,7 +53242,7 @@
           <t>CLUB_S1982_83_0126</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53251,7 +53262,7 @@
           <t>CLUB_S1982_83_0146</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53271,7 +53282,7 @@
           <t>CLUB_S1982_83_0194</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53291,7 +53302,7 @@
           <t>CLUB_S1982_83_0201</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53311,7 +53322,7 @@
           <t>CLUB_S1982_83_0218</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53331,7 +53342,7 @@
           <t>CLUB_S1982_83_0224</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -53351,7 +53362,7 @@
           <t>CLUB_S1982_83_0230</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53371,7 +53382,7 @@
           <t>CLUB_S1982_83_0236</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: city 'ZNZZ Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53391,7 +53402,7 @@
           <t>CLUB_S1982_83_0241</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -53411,7 +53422,7 @@
           <t>CLUB_S1982_83_0244</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53431,7 +53442,7 @@
           <t>CLUB_S1982_83_0252</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53451,7 +53462,7 @@
           <t>CLUB_S1982_83_0256</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53471,7 +53482,7 @@
           <t>CLUB_S1982_83_0264</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -53491,7 +53502,7 @@
           <t>CLUB_S1982_83_0282</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53511,7 +53522,7 @@
           <t>CLUB_S1982_83_0284</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53531,7 +53542,7 @@
           <t>CLUB_S1982_83_0303</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53551,7 +53562,7 @@
           <t>CLUB_S1982_83_0336</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
@@ -53571,7 +53582,7 @@
           <t>CLUB_S1982_83_0349</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -53591,7 +53602,7 @@
           <t>CLUB_S1982_83_0356</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -53611,11 +53622,37 @@
           <t>CLUB_S1982_83_0403</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Kvalifikace o 1. CHL (celostátní) · NODE_S1982_83_0002</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HC Dukla Trenčín, TJ DS Olomouc), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F37"/>

--- a/data/S1982_83_FINAL.xlsx
+++ b/data/S1982_83_FINAL.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,6 +121,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -16631,7 +16634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17137,6 +17140,23 @@
         </is>
       </c>
       <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0002</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HC Dukla Trenčín, TJ DS Olomouc), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -53642,7 +53662,7 @@
           <t>Kvalifikace o 1. CHL (celostátní) · NODE_S1982_83_0002</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (HC Dukla Trenčín, TJ DS Olomouc), chybí výsledek / odveta  [torzo-audit]</t>
         </is>

--- a/data/S1982_83_FINAL.xlsx
+++ b/data/S1982_83_FINAL.xlsx
@@ -18138,7 +18138,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30_Praha L30</t>
+          <t>Praha, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -18185,7 +18185,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -18269,7 +18269,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30_Praha L30 Základní část</t>
+          <t>Praha, 3. úroveň (krajský přebor), Základní část</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30_Praha L30 finále</t>
+          <t>Praha, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30_Praha L30 o udržení</t>
+          <t>Praha, 3. úroveň (krajský přebor) o udržení</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -18444,7 +18444,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30_Středočeský L30</t>
+          <t>Středočeský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -18538,7 +18538,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 základní část</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), základní část</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 finále</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 o umístění</t>
+          <t>Středočeský, 3. úroveň (krajský přebor) o umístění</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 KP II.třídy</t>
+          <t>Středočeský, 3. úroveň (krajský přebor) KP II.třídy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -18745,7 +18745,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina A</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina B</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina C</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Středočeský Kvalifikace o KP II.třídy</t>
+          <t>Středočeský Kvalifikace o KP II.třídy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -18923,7 +18923,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina A</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina B</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 finále</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina C</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina C</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -19109,7 +19109,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina D</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina D</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -19156,7 +19156,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30 Základní část</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor), Základní část</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30 finále</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30 o umístění</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor) o umístění</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30 II.třída</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor) II.třída</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Západočeský L30</t>
+          <t>Západočeský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -19546,7 +19546,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Západočeský L30 II.třída</t>
+          <t>Západočeský, 3. úroveň (krajský přebor) II.třída</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -19593,7 +19593,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Západočeský L30 skupina A</t>
+          <t>Západočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -19640,7 +19640,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Západočeský L30 skupina B</t>
+          <t>Západočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Západočeský L30 skupina C</t>
+          <t>Západočeský, 3. úroveň (krajský přebor), skupina C</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Západočeský kvalifikace o I.třídu</t>
+          <t>Západočeský kvalifikace o I.třídu</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -19781,7 +19781,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Severočeský L30</t>
+          <t>Severočeský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 Základní část</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), Základní část</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -19935,7 +19935,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 skupina A</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 skupina B</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 finále</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -20084,7 +20084,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 O 7.-12.místo</t>
+          <t>Severočeský, 3. úroveň (krajský přebor) O 7.-12.místo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 finále</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Východočeský L30</t>
+          <t>Východočeský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -20288,7 +20288,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Východočeský L30 základní část A</t>
+          <t>Východočeský, 3. úroveň (krajský přebor), základní část A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Východočeský L30 základní část B</t>
+          <t>Východočeský, 3. úroveň (krajský přebor), základní část B</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Východočeský L30 finále</t>
+          <t>Východočeský, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Východočeský L30 skupina o záchranu</t>
+          <t>Východočeský, 3. úroveň (krajský přebor), skupina o záchranu</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Východočeský L30 skupina A</t>
+          <t>Východočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -20560,7 +20560,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Východočeský L30 skupina B</t>
+          <t>Východočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Východočeský Kvalifikace</t>
+          <t>Východočeský Kvalifikace</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -20701,7 +20701,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina A</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -20795,7 +20795,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina B</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 finále</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -20892,7 +20892,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina A o udržení</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina A o udržení</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -20942,7 +20942,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina B o udržení</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina B o udržení</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina A</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina B</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina C</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina C</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -21118,7 +21118,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina A finále</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina A finále</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -21168,7 +21168,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina A o umístění</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina A o umístění</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -21223,7 +21223,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina B finále</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina B finále</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina B o umístění</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina B o umístění</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina C finále</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina C finále</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina C o umístění</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina C o umístění</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -21433,7 +21433,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 základní skupina</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor), základní skupina</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -21587,7 +21587,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 finále</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 o udržení</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor) o udržení</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -21692,7 +21692,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 II.třída</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor) II.třída</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 skupina A</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 Skupina B</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor), Skupina B</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30_SVK L30</t>
+          <t>Slovensko, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -21870,7 +21870,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30_SVK L30 Východoslovenský kraj</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) Východoslovenský kraj</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -21912,7 +21912,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>30_SVK L30 skupina východ</t>
+          <t>Slovensko, 3. úroveň (krajský přebor), skupina východ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -21954,7 +21954,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30_SVK L30 skupina západ</t>
+          <t>Slovensko, 3. úroveň (krajský přebor), skupina západ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -21996,7 +21996,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30_SVK L30 finále</t>
+          <t>Slovensko, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -22046,7 +22046,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30_SVK L30 Západoslovenský kraj</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) Západoslovenský kraj</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -22088,7 +22088,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>30_SVK L30 základní část</t>
+          <t>Slovensko, 3. úroveň (krajský přebor), základní část</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -22148,7 +22148,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>30_SVK L30 finále</t>
+          <t>Slovensko, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>30_SVK L30 o udržení</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) o udržení</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -22248,7 +22248,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>30_SVK L30 Středoslovenský kraj</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) Středoslovenský kraj</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>30_SVK L30 Středoslovenský krajský přebor</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) Středoslovenský krajský přebor</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -22332,7 +22332,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>30_SVK L30 Východoslovenský krajský přebor</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) Východoslovenský krajský přebor</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>30_SVK L30 Západoslovenský krajský přebor</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) Západoslovenský krajský přebor</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 Krajský přebor II.třídy</t>
+          <t>Východočeský, 4. úroveň Krajský přebor II.třídy</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Krajský přebor II.třídy</t>
+          <t>Jihomoravský, 4. úroveň Krajský přebor II.třídy</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">

--- a/data/S1982_83_FINAL.xlsx
+++ b/data/S1982_83_FINAL.xlsx
@@ -3433,7 +3433,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -48049,7 +48049,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -48127,7 +48127,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -48205,7 +48205,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -48283,7 +48283,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -48361,7 +48361,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -48439,7 +48439,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -48517,7 +48517,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -48595,7 +48595,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -48673,7 +48673,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -48751,7 +48751,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -48829,7 +48829,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -48912,7 +48912,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -51405,7 +51405,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -55042,7 +55042,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -55120,7 +55120,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -55198,7 +55198,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -55276,7 +55276,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -55349,7 +55349,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -55427,7 +55427,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -55510,7 +55510,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -55588,7 +55588,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -56055,7 +56055,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -56211,7 +56211,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -77428,7 +77428,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
